--- a/WAIFF_Refinement_Log.xlsx
+++ b/WAIFF_Refinement_Log.xlsx
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1422,26 +1422,230 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Offer / product</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sell Cannes 2027 (6-7 Apr) + named editions to global sponsors. India edition (December) is the add-on for India-focused brands.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>The India edition has no public date, venue or organizer, so brand teams cannot approve it. Venues replied only to sell rooms.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>523 companies emailed, 0 sponsor money conversations</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Targeting</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Prioritise companies that already pay for film festivals, Bollywood awards or Cannes, or are entering India with money. De-prioritise AI startups and hardware giants.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Startup replies cite no budget (Wonder, Cascadeur, Ideogram, Hedra). Hardware majors decline via support desks.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>New 70-company list built on this rule (WAIFF_70_Targets_Sep24.xlsx)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Organizer definition</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Organizers = companies whose business is events or festival IP (Serendipity, Teamwork Arts, STIR, IndiaJoy, BTS, AIM). Not industrial groups.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MRF: 'doesn't fit into our plans'. Tyre, steel and pharma company secretaries were asked to pay EUR50k.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>20 organizer candidates rebuilt</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Message errors</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Check merge fields. Remove false urgency, 'Apple Global', the Cannes Film Festival venue line and long AI-toned replies.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>'Cascadeur's India edition' merge bug (13-14 Sep). Hedra CEO flagged an AI-written reply. 1,500-word Kimi rebuttal.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Templates rewritten (Templates sheet)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Follow-through</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Reply to every human answer within 24h, before any new outreach.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NESCO (22 Sep), Cascadeur (14 Sep), Getty (11 Sep), Novotel (18 Sep), Trident (11 Sep) were left unanswered.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Warm-leads sheet created</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ask WAiFF HQ for an @worldaifilmfestival.com mailbox and an appointment letter.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Personal gmail.com is rejected by many B2B forms and weakens trust with big brands.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pending Aditya / Marco</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DNC compliance</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Stop contacting existing WAiFF partners (TF1, Fnac, Station F, CapCut, MiniMax, CloudWalk/Brazil).</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>All were emailed between 13 and 19 Sep.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Flagged in the follow-up audit as C</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WAIFF_Refinement_Log.xlsx
+++ b/WAIFF_Refinement_Log.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5 Sep 2026, end of day. Rebuilt from 140 Gmail sends, 141 LinkedIn profiles, and 36 form attempts logged to date. Update this sheet whenever a new lesson lands or numbers move enough to change the guidance below.</t>
+          <t>24 Sep 2026. Superseded in detail by WAIFF_Email_Quality_Playbook_Sep24.md (read that first). Rebuilt from a Gmail audit of ~990 WAiFF emails to ~478 companies.</t>
         </is>
       </c>
     </row>
@@ -518,14 +518,12 @@
     <row r="5" ht="120" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>TODAY'S REAL NUMBERS (5 Sep 2026)</t>
+          <t>TODAY'S REAL NUMBERS (24 Sep 2026, recomputed from Gmail)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Gmail: 140 sends logged total. 6 bounced (4.3%) - just above the brief's 3% warning line, needs tightening. 4 confirmed replies (2.9% blended) - but this blends two very different cohorts (see next row), so treat it as a floor, not the real signal.
-LinkedIn: 141 profiles logged. Only 15 confirmed accepted (6 'Accepted' + 9 'Accepted (already 1st-degree)'). 87 are still 'Pending' and 39 'Not sent yet' - meaning most connection requests have not actually been sent by Aditya yet. 2 replies so far (Anupreet Singh/Supa, Frenil Solani/Balaji Telefilms).
-CORRECTION: the old Success Rate Snapshot claimed '94% acceptance, 133/141' - that number was wrong. Re-checked directly against the Status column today; corrected figures are above. Always re-derive this from the actual Status column, never carry a stale summary number forward.</t>
+          <t>~990 emails (570 first touches, 379 follow-ups) to ~478 companies. Bounce: 8.9% of first touches (limit 3%). Human replies: 30 companies (6.3%), engaged 13 (2.7%), proposals 0, money 0. Only 4.6% of first touches went to a partnerships/sponsorship inbox.</t>
         </is>
       </c>
     </row>
@@ -611,9 +609,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Two SPECIFIC, current facts per company - one present initiative and one recent or upcoming launch - never a shared category-level paragraph reused across similar companies in the same batch. This was Aditya's own direct correction mid-campaign and it holds: reused lines read as templated.
-Structure, every time: specific appreciation -&gt; who Aditya is + what WAiFF is (only facts from brief section 2) -&gt; why this company specifically -&gt; ask for a call, IST timezone stated.
-Under 180 words for email, 120 for LinkedIn, 280 characters for a connection note. No em dashes, no semicolons, no 'moreover/furthermore/in today's landscape'. Never promise a tier, price, benefit, audience number, or Marco Landi's attendance. Never send the Canva/deck link, in any channel, ever.</t>
+          <t>See WAIFF_Email_Quality_Playbook_Sep24.md Parts B, E and J. Subject 2-5 words, body 50-90 words: dated fact about them, one WAiFF fact, one idea, one proof point, interest question. Verified facts only (Part C). Replies within 24h, 120 words, calendar invite sent by us.</t>
         </is>
       </c>
     </row>
@@ -658,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1641,6 +1637,198 @@
         </is>
       </c>
       <c r="F31" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Targeting</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Write only to named owners of budget, activation or new IP. Stop press@, support@, care@, info@, investor relations and company-secretary inboxes.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Gmail audit: only 26 of 570 first touches (4.6%) went to a partnerships/sponsorship/BD address. Most human replies were hotels selling to us or support bots.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>30 human replies from ~478 companies (6.3%), 13 engaged (2.7%), 0 proposals (recomputed from Gmail 24 Sep).</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Warm leads</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Answer every human reply within 24h before new outreach, in 120 words or less, with a calendar invite sent by us. Never argue with a decline.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>13 engaged prospects produced 0 proposals. Cascadeur waited 10 days for a price answer. Cooke got 1,100 words after 82h. Hedra CEO flagged AI-written text.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>8 warm leads listed in the Email Quality Playbook, Part L.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Copy</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New first-email standard: 2-5 word subject, 50-90 words, dated fact about them, one idea, one proof point, interest question. 34 finished drafts in the v5 companies workbook.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>First emails ran 136 to 1,008 words at college reading level, ask always last, 72% of subjects had em dashes, fake "Re:" on 274 follow-ups.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Not yet sent. Measure reply rate on the first 60 v5 sends against the 2.7% baseline.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Corrected WAiFF facts in the brief: "more than 5,000 films from over 80 countries", 2025 was Nice, third edition (not third Cannes), Gong Li = President, no Hollywood names, no "15+ countries/30+ cities".</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Fact book built from the official programme, rules, deck and press found about 15 wrong claims in sent mail and in the brief itself.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Brief section 2 corrections block added.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sending</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20-40 new emails a day, weekdays, 8-11am recipient time, schedule-send, no bursts. Never re-mail a bounced address.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>40% of first touches left 00:00-04:00 IST, 50% on weekends; 135 emails in 4 minutes on a Sunday; 8.9% bounce rate; 13 dead addresses re-mailed up to 4 times.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Target list</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Replaced 7 weak sponsors (ad-tech, Dassault, Duolingo, PW) and 5 small organizers with verified companies that already sponsor festivals (Orange, Renault, HUMAIN, Kia, Motorola, Dropbox...) or can run a December edition (Aptech/MAAC, Publicis, Noida Film City, SIIMA).</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Engaged replies came almost only from companies whose product touches filmmakers/creators or who run events. 88 luxury/finance emails got 0 engaged replies.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>v5 lists: 30 sponsors, 23 organizers, 100 LinkedIn profiles.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Active standard</t>
         </is>
